--- a/public/itinerary-template.xlsx
+++ b/public/itinerary-template.xlsx
@@ -1,48 +1,112 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <bookViews>
+    <workbookView/>
+  </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
     <sheet name="안내" sheetId="2" r:id="rId2"/>
+    <sheet name="설명" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">날짜</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">일차</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">시간</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">종류</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">내용</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">장소</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">메모</t>
         </is>
@@ -572,19 +636,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">항목</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">내용</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(추가)</t>
         </is>
@@ -681,6 +752,152 @@
       <c r="B8" t="inlineStr">
         <is>
           <t xml:space="preserve">호핑투어 날은 수영복을 미리 입고 나오세요</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="78" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기조톡 일정표 양식 — 사용법</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[일정] 시트의 칸만 채우고 저장한 뒤, 카톡·텔레그램으로 보내면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">날짜와 일차는 그날 첫 줄에만 적으세요. 아래 줄은 비워두면 이어집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">종류에 쓸 수 있는 말: 집합 항공 이동 식사 투어 숙소 쇼핑 자유 기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(여기 없는 말을 쓰면 "기타" 로 들어갑니다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장소 칸을 채우면 그 일정에 [기사에게 보여주기] 버튼이 생깁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기사에게 폰을 그대로 보여주는 화면입니다. 현지 표기(영문)로 적어주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신청자만 가는 옵션투어는 내용 앞에 "(옵션)" 을 붙여주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안 붙이면 신청하지 않은 분에게도 곧 출발한다고 알림이 갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메모에 적은 전화번호(+63 32 342 8888)는 앱에서 눌러 바로 걸립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[안내] 시트에는 제목·기간·연락처·특이사항을 적습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">연락처와 특이사항은 줄을 늘려 여러 개 적을 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">※</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시트 이름(일정·안내)은 바꾸지 마세요.</t>
         </is>
       </c>
     </row>

--- a/public/itinerary-template.xlsx
+++ b/public/itinerary-template.xlsx
@@ -771,7 +771,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">기조톡 일정표 양식 — 사용법</t>
+          <t xml:space="preserve">GIJO Tour 일정표 양식 — 사용법</t>
         </is>
       </c>
     </row>
